--- a/data/gold/results/table_s5_dk.xlsx
+++ b/data/gold/results/table_s5_dk.xlsx
@@ -388,13 +388,13 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>6293.083293176651</v>
+        <v>4875.04189130478</v>
       </c>
       <c r="C2">
-        <v>85752.01480508699</v>
+        <v>64720.67119886602</v>
       </c>
       <c r="D2">
-        <v>7.338700213027918</v>
+        <v>7.532434075544933</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -402,13 +402,13 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>3129.438454051277</v>
+        <v>5595.226019299745</v>
       </c>
       <c r="C3">
-        <v>47233.92252096916</v>
+        <v>81896.03408341862</v>
       </c>
       <c r="D3">
-        <v>6.625404554665104</v>
+        <v>6.832108638619173</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -416,13 +416,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>57.49180799643617</v>
+        <v>43.01963532551069</v>
       </c>
       <c r="C4">
-        <v>1070.441660416759</v>
+        <v>883.0636615745001</v>
       </c>
       <c r="D4">
-        <v>5.37084925992629</v>
+        <v>4.871634650757432</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -430,13 +430,13 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>3515.40410784478</v>
+        <v>3833.21048095657</v>
       </c>
       <c r="C5">
-        <v>76743.82483988514</v>
+        <v>86351.7602835304</v>
       </c>
       <c r="D5">
-        <v>4.580699639585545</v>
+        <v>4.439064668016577</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -444,13 +444,13 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1067.400314520272</v>
+        <v>1481.801246893921</v>
       </c>
       <c r="C6">
-        <v>23288.33763838921</v>
+        <v>23660.11065987919</v>
       </c>
       <c r="D6">
-        <v>4.583411367073007</v>
+        <v>6.26286693327531</v>
       </c>
     </row>
   </sheetData>
